--- a/StructureDefinition-ng-claim.xlsx
+++ b/StructureDefinition-ng-claim.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/StructureDefinition/ng-claim</t>
+    <t>https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-02T14:19:18+01:00</t>
+    <t>2025-09-10T08:54:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -604,7 +604,7 @@
     <t>Claim.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://dhin.org/2025Connectathon/StructureDefinition/NgPatient)
+    <t xml:space="preserve">Reference(https://www.dhin-hie.org/IGs/StructureDefinition/NgPatient)
 </t>
   </si>
   <si>
@@ -968,7 +968,7 @@
     <t>Claim.payee.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://dhin.org/2025Connectathon/StructureDefinition/NgPractitioner)
+    <t xml:space="preserve">Reference(https://www.dhin-hie.org/IGs/StructureDefinition/NgPractitioner)
 </t>
   </si>
   <si>
@@ -1489,7 +1489,7 @@
     <t>procedureReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://dhin.org/2025Connectathon/StructureDefinition/ng-claim-procedure)
+    <t xml:space="preserve">Reference(https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim-procedure)
 </t>
   </si>
   <si>
@@ -1624,7 +1624,7 @@
     <t>Claim.insurance.claimResponse</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://dhin.org/2025Connectathon/StructureDefinition/ng-claimresponse)
+    <t xml:space="preserve">Reference(https://www.dhin-hie.org/IGs/StructureDefinition/ng-claimresponse)
 </t>
   </si>
   <si>
@@ -2508,7 +2508,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.52734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
